--- a/master/result/67_重生女强_职场逆袭传奇/67_重生女强_职场逆袭传奇.xlsx
+++ b/master/result/67_重生女强_职场逆袭传奇/67_重生女强_职场逆袭传奇.xlsx
@@ -397,588 +397,745 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:D52"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文含义</v>
+        <v>词性</v>
+      </c>
+      <c r="D1" t="str">
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>June</v>
       </c>
       <c r="B2" t="str">
-        <v>June</v>
+        <v>/June/</v>
       </c>
       <c r="C2" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>六月</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>Wednesday</v>
       </c>
       <c r="B3" t="str">
-        <v>Wednesday</v>
+        <v>/Wednesday/</v>
       </c>
       <c r="C3" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>星期三</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>childhood</v>
       </c>
       <c r="B4" t="str">
-        <v>childhood</v>
+        <v>/ˈtʃaɪldhʊd/</v>
       </c>
       <c r="C4" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>童年</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>bully</v>
       </c>
       <c r="B5" t="str">
-        <v>bully</v>
+        <v>/bully/</v>
       </c>
       <c r="C5" t="str">
+        <v>adv.</v>
+      </c>
+      <c r="D5" t="str">
         <v>恃强欺弱者</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>tragic</v>
       </c>
       <c r="B6" t="str">
-        <v>tragic</v>
+        <v>/tragic/</v>
       </c>
       <c r="C6" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D6" t="str">
         <v>悲剧的</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>numb</v>
       </c>
       <c r="B7" t="str">
-        <v>numb</v>
+        <v>/numb/</v>
       </c>
       <c r="C7" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D7" t="str">
         <v>麻木的</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>headquarters</v>
       </c>
       <c r="B8" t="str">
-        <v>headquarters</v>
+        <v>/headquarters/</v>
       </c>
       <c r="C8" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>总部</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>appeal</v>
       </c>
       <c r="B9" t="str">
-        <v>appeal</v>
+        <v>/appeal/</v>
       </c>
       <c r="C9" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>呼吁</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>again</v>
       </c>
       <c r="B10" t="str">
-        <v>again</v>
+        <v>/again/</v>
       </c>
       <c r="C10" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>再次</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>cognitive</v>
       </c>
       <c r="B11" t="str">
-        <v>cognitive</v>
+        <v>/cognitive/</v>
       </c>
       <c r="C11" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D11" t="str">
         <v>认知的</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>prototype</v>
       </c>
       <c r="B12" t="str">
-        <v>prototype</v>
+        <v>/prototype/</v>
       </c>
       <c r="C12" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D12" t="str">
         <v>原型</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>a</v>
       </c>
       <c r="B13" t="str">
-        <v>a</v>
+        <v>/a/</v>
       </c>
       <c r="C13" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>一个</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>blouse</v>
       </c>
       <c r="B14" t="str">
-        <v>blouse</v>
+        <v>/blaʊz/</v>
       </c>
       <c r="C14" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>女衬衣</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>dimension</v>
       </c>
       <c r="B15" t="str">
-        <v>dimension</v>
+        <v>/dimension/</v>
       </c>
       <c r="C15" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>尺寸</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>bold</v>
       </c>
       <c r="B16" t="str">
-        <v>bold</v>
+        <v>/bold/</v>
       </c>
       <c r="C16" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D16" t="str">
         <v>大胆的</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>creative</v>
       </c>
       <c r="B17" t="str">
-        <v>creative</v>
+        <v>/kriˈeɪtɪv/</v>
       </c>
       <c r="C17" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D17" t="str">
         <v>有创造力的</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>virtue</v>
       </c>
       <c r="B18" t="str">
-        <v>virtue</v>
+        <v>/virtue/</v>
       </c>
       <c r="C18" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D18" t="str">
         <v>美德</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>document</v>
       </c>
       <c r="B19" t="str">
-        <v>document</v>
+        <v>/document/</v>
       </c>
       <c r="C19" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D19" t="str">
         <v>公文</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>subsidy</v>
       </c>
       <c r="B20" t="str">
-        <v>subsidy</v>
+        <v>/subsidy/</v>
       </c>
       <c r="C20" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>补助金</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>grateful</v>
       </c>
       <c r="B21" t="str">
-        <v>grateful</v>
+        <v>/grateful/</v>
       </c>
       <c r="C21" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D21" t="str">
         <v>感激的</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>they</v>
       </c>
       <c r="B22" t="str">
-        <v>they</v>
+        <v>/they/</v>
       </c>
       <c r="C22" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D22" t="str">
         <v>他们</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>refuse</v>
       </c>
       <c r="B23" t="str">
-        <v>refuse</v>
+        <v>/rɪˈfjuːz/</v>
       </c>
       <c r="C23" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D23" t="str">
         <v>拒绝</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>charter</v>
       </c>
       <c r="B24" t="str">
+        <v>/charter/</v>
+      </c>
+      <c r="C24" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D24" t="str">
+        <v>宪章</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>suspend</v>
+      </c>
+      <c r="B25" t="str">
+        <v>/səˈspend/</v>
+      </c>
+      <c r="C25" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D25" t="str">
+        <v>暂停</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>hook</v>
+      </c>
+      <c r="B26" t="str">
+        <v>/hook/</v>
+      </c>
+      <c r="C26" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D26" t="str">
+        <v>钩</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>segregate</v>
+      </c>
+      <c r="B27" t="str">
+        <v>/segregate/</v>
+      </c>
+      <c r="C27" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D27" t="str">
+        <v>隔离</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>dine</v>
+      </c>
+      <c r="B28" t="str">
+        <v>/dine/</v>
+      </c>
+      <c r="C28" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D28" t="str">
+        <v>吃饭</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>pear</v>
+      </c>
+      <c r="B29" t="str">
+        <v>/pear/</v>
+      </c>
+      <c r="C29" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D29" t="str">
+        <v>梨子</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>virtual</v>
+      </c>
+      <c r="B30" t="str">
+        <v>/virtual/</v>
+      </c>
+      <c r="C30" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D30" t="str">
+        <v>实际上的</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>from</v>
+      </c>
+      <c r="B31" t="str">
+        <v>/from/</v>
+      </c>
+      <c r="C31" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D31" t="str">
+        <v>从</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>gymnasium</v>
+      </c>
+      <c r="B32" t="str">
+        <v>/gymnasium/</v>
+      </c>
+      <c r="C32" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D32" t="str">
+        <v>体育馆</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>amid</v>
+      </c>
+      <c r="B33" t="str">
+        <v>/amid/</v>
+      </c>
+      <c r="C33" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D33" t="str">
+        <v>在...中间</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>bleak</v>
+      </c>
+      <c r="B34" t="str">
+        <v>/bleak/</v>
+      </c>
+      <c r="C34" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D34" t="str">
+        <v>荒凉的</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>mind</v>
+      </c>
+      <c r="B35" t="str">
+        <v>/maɪnd/</v>
+      </c>
+      <c r="C35" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D35" t="str">
+        <v>精神</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>faculty</v>
+      </c>
+      <c r="B36" t="str">
+        <v>/faculty/</v>
+      </c>
+      <c r="C36" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D36" t="str">
+        <v>学院</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>appreciate</v>
+      </c>
+      <c r="B37" t="str">
+        <v>/əˈpriːʃieɪt/</v>
+      </c>
+      <c r="C37" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D37" t="str">
+        <v>感激</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>safety</v>
+      </c>
+      <c r="B38" t="str">
+        <v>/safety/</v>
+      </c>
+      <c r="C38" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D38" t="str">
+        <v>安全</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>stream</v>
+      </c>
+      <c r="B39" t="str">
+        <v>/stream/</v>
+      </c>
+      <c r="C39" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D39" t="str">
+        <v>溪流</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>travel</v>
+      </c>
+      <c r="B40" t="str">
+        <v>/ˈtrævəl/</v>
+      </c>
+      <c r="C40" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D40" t="str">
+        <v>旅行</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
         <v>charter</v>
       </c>
-      <c r="C24" t="str">
-        <v>宪章</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25" t="str">
-        <v>suspend</v>
-      </c>
-      <c r="C25" t="str">
-        <v>暂停</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" t="str">
-        <v>hook</v>
-      </c>
-      <c r="C26" t="str">
-        <v>钩</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27" t="str">
-        <v>segregate</v>
-      </c>
-      <c r="C27" t="str">
-        <v>隔离</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28" t="str">
-        <v>dine</v>
-      </c>
-      <c r="C28" t="str">
-        <v>吃饭</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29" t="str">
-        <v>pear</v>
-      </c>
-      <c r="C29" t="str">
-        <v>梨子</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30" t="str">
-        <v>virtual</v>
-      </c>
-      <c r="C30" t="str">
-        <v>实际上的</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31" t="str">
-        <v>from</v>
-      </c>
-      <c r="C31" t="str">
-        <v>从</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32" t="str">
-        <v>gymnasium</v>
-      </c>
-      <c r="C32" t="str">
-        <v>体育馆</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" t="str">
-        <v>amid</v>
-      </c>
-      <c r="C33" t="str">
-        <v>在...中间</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" t="str">
-        <v>bleak</v>
-      </c>
-      <c r="C34" t="str">
-        <v>荒凉的</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35" t="str">
-        <v>mind</v>
-      </c>
-      <c r="C35" t="str">
-        <v>精神</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36" t="str">
-        <v>faculty</v>
-      </c>
-      <c r="C36" t="str">
-        <v>学院</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37" t="str">
-        <v>appreciate</v>
-      </c>
-      <c r="C37" t="str">
-        <v>感激</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="str">
-        <v>safety</v>
-      </c>
-      <c r="C38" t="str">
-        <v>安全</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" t="str">
-        <v>stream</v>
-      </c>
-      <c r="C39" t="str">
-        <v>溪流</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="str">
-        <v>travel</v>
-      </c>
-      <c r="C40" t="str">
-        <v>旅行</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <v>40</v>
-      </c>
       <c r="B41" t="str">
-        <v>charter</v>
+        <v>/charter/</v>
       </c>
       <c r="C41" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D41" t="str">
         <v>租用</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>straw</v>
       </c>
       <c r="B42" t="str">
-        <v>straw</v>
+        <v>/straw/</v>
       </c>
       <c r="C42" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D42" t="str">
         <v>稻草</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>fun</v>
       </c>
       <c r="B43" t="str">
-        <v>fun</v>
+        <v>/fun/</v>
       </c>
       <c r="C43" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D43" t="str">
         <v>玩笑</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>trap</v>
       </c>
       <c r="B44" t="str">
-        <v>trap</v>
+        <v>/trap/</v>
       </c>
       <c r="C44" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D44" t="str">
         <v>陷阱</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>vote</v>
       </c>
       <c r="B45" t="str">
-        <v>vote</v>
+        <v>/vote/</v>
       </c>
       <c r="C45" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D45" t="str">
         <v>投票</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>dissolve</v>
       </c>
       <c r="B46" t="str">
-        <v>dissolve</v>
+        <v>/dissolve/</v>
       </c>
       <c r="C46" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D46" t="str">
         <v>溶解</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>continue</v>
       </c>
       <c r="B47" t="str">
-        <v>continue</v>
+        <v>/kənˈtɪnjuː/</v>
       </c>
       <c r="C47" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D47" t="str">
         <v>继续</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>absorb</v>
       </c>
       <c r="B48" t="str">
-        <v>absorb</v>
+        <v>/əbˈzɔːb/</v>
       </c>
       <c r="C48" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D48" t="str">
         <v>吸收</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>verify</v>
       </c>
       <c r="B49" t="str">
-        <v>verify</v>
+        <v>/verify/</v>
       </c>
       <c r="C49" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D49" t="str">
         <v>证实</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>repertoire</v>
       </c>
       <c r="B50" t="str">
-        <v>repertoire</v>
+        <v>/repertoire/</v>
       </c>
       <c r="C50" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D50" t="str">
         <v>全部剧目</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>medicine</v>
       </c>
       <c r="B51" t="str">
-        <v>medicine</v>
+        <v>/medicine/</v>
       </c>
       <c r="C51" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D51" t="str">
         <v>医学</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52">
-        <v>51</v>
+      <c r="A52" t="str">
+        <v>eclipse</v>
       </c>
       <c r="B52" t="str">
-        <v>eclipse</v>
+        <v>/eclipse/</v>
       </c>
       <c r="C52" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D52" t="str">
         <v>日食</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C52"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D52"/>
   </ignoredErrors>
 </worksheet>
 </file>